--- a/www_Test _new_lot_rull/fill/formlist/3_14.xlsx
+++ b/www_Test _new_lot_rull/fill/formlist/3_14.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\www_Test _new_lot_rull\fill\formlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB308A4-93CF-4AFE-A65D-F5634086BB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60DDA9F-2FA2-4D9B-8D7F-734AC36E30BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1140" windowWidth="14145" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8595" yWindow="1935" windowWidth="20535" windowHeight="9675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NEW" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="190">
   <si>
     <t>充填管理者</t>
   </si>
@@ -1888,7 +1888,7 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -2143,7 +2143,12 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="C39HrP48DmTt"/>
+    </font>
+    <font>
+      <sz val="22"/>
       <name val="C39HrP48DmTt"/>
     </font>
   </fonts>
@@ -2787,7 +2792,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2998,12 +3003,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3165,6 +3164,12 @@
     </xf>
     <xf numFmtId="177" fontId="11" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -3245,64 +3250,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -3311,33 +3337,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3640,6 +3639,18 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4007,7 +4018,7 @@
       <c r="L5" s="67"/>
     </row>
     <row r="6" spans="1:12" ht="28.5" customHeight="1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="75" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="71" t="s">
@@ -4018,46 +4029,48 @@
       <c r="E6" s="71"/>
       <c r="F6" s="72"/>
       <c r="G6" s="73"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="80"/>
+      <c r="H6" s="293" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="294"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A7" s="77"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="71" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
       <c r="E7" s="71"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="82"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="80"/>
       <c r="J7" s="68"/>
       <c r="K7" s="69"/>
       <c r="L7" s="70"/>
     </row>
     <row r="8" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A8" s="77"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="71" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="71"/>
       <c r="D8" s="71"/>
       <c r="E8" s="71"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="82"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="80"/>
       <c r="J8" s="68"/>
       <c r="K8" s="69"/>
       <c r="L8" s="70"/>
     </row>
     <row r="9" spans="1:12" ht="28.5" customHeight="1">
-      <c r="A9" s="77"/>
+      <c r="A9" s="75"/>
       <c r="B9" s="71" t="s">
         <v>16</v>
       </c>
@@ -4066,24 +4079,24 @@
       <c r="E9" s="71"/>
       <c r="F9" s="72"/>
       <c r="G9" s="73"/>
-      <c r="H9" s="74" t="str">
+      <c r="H9" s="295" t="str">
         <f>"*"&amp;"1"&amp;F9&amp;"*"</f>
         <v>*1*</v>
       </c>
-      <c r="I9" s="75"/>
+      <c r="I9" s="296"/>
       <c r="J9" s="68"/>
       <c r="K9" s="69"/>
       <c r="L9" s="70"/>
     </row>
     <row r="10" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A10" s="77"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="71" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="71"/>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
-      <c r="F10" s="76"/>
+      <c r="F10" s="74"/>
       <c r="G10" s="65"/>
       <c r="H10" s="65"/>
       <c r="I10" s="47" t="s">
@@ -4094,16 +4107,16 @@
       <c r="L10" s="70"/>
     </row>
     <row r="11" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A11" s="77"/>
+      <c r="A11" s="75"/>
       <c r="B11" s="71" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="71"/>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
       <c r="I11" s="47" t="s">
         <v>23</v>
       </c>
@@ -4112,7 +4125,7 @@
       <c r="L11" s="70"/>
     </row>
     <row r="12" spans="1:12" ht="28.5" customHeight="1">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="75" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="71" t="s">
@@ -4123,36 +4136,36 @@
       <c r="E12" s="71"/>
       <c r="F12" s="72"/>
       <c r="G12" s="73"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="75"/>
+      <c r="H12" s="295"/>
+      <c r="I12" s="296"/>
       <c r="J12" s="68"/>
       <c r="K12" s="69"/>
       <c r="L12" s="70"/>
     </row>
     <row r="13" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A13" s="77"/>
-      <c r="B13" s="89" t="s">
+      <c r="A13" s="75"/>
+      <c r="B13" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="90"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="84"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="82"/>
       <c r="J13" s="68"/>
       <c r="K13" s="69"/>
       <c r="L13" s="70"/>
     </row>
     <row r="14" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A14" s="77"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="48"/>
       <c r="G14" s="44" t="s">
         <v>33</v>
@@ -4169,16 +4182,16 @@
       <c r="L14" s="70"/>
     </row>
     <row r="15" spans="1:12" ht="27" customHeight="1">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="87"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="84"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="82"/>
       <c r="I15" s="47" t="s">
         <v>37</v>
       </c>
@@ -4187,15 +4200,15 @@
       <c r="L15" s="70"/>
     </row>
     <row r="16" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="75" t="s">
         <v>185</v>
       </c>
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="97"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="98"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="96"/>
       <c r="F16" s="58"/>
       <c r="G16" s="58" t="s">
         <v>41</v>
@@ -4209,379 +4222,379 @@
       <c r="L16" s="70"/>
     </row>
     <row r="17" spans="1:12" ht="35.25" customHeight="1">
-      <c r="A17" s="77"/>
-      <c r="B17" s="89" t="s">
+      <c r="A17" s="75"/>
+      <c r="B17" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="89"/>
+      <c r="C17" s="87"/>
       <c r="D17" s="65"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="91" t="s">
+      <c r="E17" s="91"/>
+      <c r="F17" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="92"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
       <c r="J17" s="69"/>
       <c r="K17" s="69"/>
       <c r="L17" s="70"/>
     </row>
     <row r="18" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A18" s="77"/>
-      <c r="B18" s="89" t="s">
+      <c r="A18" s="75"/>
+      <c r="B18" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="89"/>
+      <c r="C18" s="87"/>
       <c r="D18" s="65"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="91" t="s">
+      <c r="E18" s="91"/>
+      <c r="F18" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
-      <c r="I18" s="92"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
       <c r="J18" s="69"/>
       <c r="K18" s="69"/>
       <c r="L18" s="70"/>
     </row>
     <row r="19" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A19" s="77"/>
-      <c r="B19" s="89" t="s">
+      <c r="A19" s="75"/>
+      <c r="B19" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="89"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="65"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="91" t="s">
+      <c r="E19" s="91"/>
+      <c r="F19" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="92"/>
-      <c r="H19" s="92"/>
-      <c r="I19" s="92"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
       <c r="J19" s="69"/>
       <c r="K19" s="69"/>
       <c r="L19" s="70"/>
     </row>
     <row r="20" spans="1:12" ht="21" customHeight="1">
-      <c r="A20" s="77"/>
-      <c r="B20" s="89" t="s">
+      <c r="A20" s="75"/>
+      <c r="B20" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="89"/>
+      <c r="C20" s="87"/>
       <c r="D20" s="65"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="91" t="s">
+      <c r="E20" s="91"/>
+      <c r="F20" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="92"/>
-      <c r="H20" s="92"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="94"/>
-      <c r="L20" s="95"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="93"/>
     </row>
     <row r="21" spans="1:12" ht="21" customHeight="1">
-      <c r="A21" s="77"/>
-      <c r="B21" s="89" t="s">
+      <c r="A21" s="75"/>
+      <c r="B21" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="89"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="65"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="91" t="s">
+      <c r="E21" s="91"/>
+      <c r="F21" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="92"/>
-      <c r="H21" s="92"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="95"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="93"/>
     </row>
     <row r="22" spans="1:12" ht="21" customHeight="1">
-      <c r="A22" s="77"/>
-      <c r="B22" s="89" t="s">
+      <c r="A22" s="75"/>
+      <c r="B22" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="89"/>
+      <c r="C22" s="87"/>
       <c r="D22" s="65"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="99" t="e">
+      <c r="E22" s="87"/>
+      <c r="F22" s="97" t="e">
         <f>F11-H14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="100"/>
-      <c r="H22" s="100"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
       <c r="I22" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="J22" s="94"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="95"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="93"/>
     </row>
     <row r="23" spans="1:12" ht="21" customHeight="1">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="102" t="s">
         <v>53</v>
       </c>
       <c r="B23" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="78" t="s">
+      <c r="C23" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="108"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="106"/>
       <c r="I23" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="J23" s="94"/>
-      <c r="K23" s="94"/>
-      <c r="L23" s="95"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="93"/>
     </row>
     <row r="24" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A24" s="105"/>
-      <c r="B24" s="109" t="s">
+      <c r="A24" s="103"/>
+      <c r="B24" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="109"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="108"/>
       <c r="I24" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="94"/>
-      <c r="K24" s="94"/>
-      <c r="L24" s="95"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="93"/>
     </row>
     <row r="25" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A25" s="118" t="s">
+      <c r="A25" s="116" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="119" t="s">
+      <c r="B25" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="120" t="s">
+      <c r="C25" s="117"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="F25" s="91"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="108"/>
       <c r="I25" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="J25" s="122" t="s">
+      <c r="J25" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="K25" s="123"/>
-      <c r="L25" s="124"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="122"/>
     </row>
     <row r="26" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A26" s="77"/>
-      <c r="B26" s="125" t="s">
+      <c r="A26" s="75"/>
+      <c r="B26" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="125"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="121"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="119"/>
       <c r="F26" s="54"/>
       <c r="G26" s="53" t="s">
         <v>41</v>
       </c>
       <c r="H26" s="48"/>
-      <c r="I26" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="101"/>
-      <c r="K26" s="101"/>
-      <c r="L26" s="102"/>
+      <c r="I26" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="99"/>
+      <c r="K26" s="99"/>
+      <c r="L26" s="100"/>
     </row>
     <row r="27" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A27" s="77"/>
-      <c r="B27" s="89" t="s">
+      <c r="A27" s="75"/>
+      <c r="B27" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="89"/>
+      <c r="C27" s="87"/>
       <c r="D27" s="65"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="127">
+      <c r="E27" s="87"/>
+      <c r="F27" s="125">
         <v>1.9</v>
       </c>
-      <c r="G27" s="128"/>
-      <c r="H27" s="129"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="127"/>
       <c r="I27" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="J27" s="101"/>
-      <c r="K27" s="101"/>
-      <c r="L27" s="102"/>
+      <c r="J27" s="99"/>
+      <c r="K27" s="99"/>
+      <c r="L27" s="100"/>
     </row>
     <row r="28" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A28" s="77"/>
-      <c r="B28" s="103" t="s">
+      <c r="A28" s="75"/>
+      <c r="B28" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="103"/>
+      <c r="C28" s="101"/>
       <c r="D28" s="65"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="76" t="s">
+      <c r="E28" s="101"/>
+      <c r="F28" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
       <c r="J28" s="69"/>
       <c r="K28" s="69"/>
       <c r="L28" s="70"/>
     </row>
     <row r="29" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A29" s="77"/>
-      <c r="B29" s="89" t="s">
+      <c r="A29" s="75"/>
+      <c r="B29" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="89"/>
+      <c r="C29" s="87"/>
       <c r="D29" s="65"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="76" t="s">
+      <c r="E29" s="87"/>
+      <c r="F29" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81"/>
-      <c r="J29" s="101"/>
-      <c r="K29" s="101"/>
-      <c r="L29" s="102"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="99"/>
+      <c r="K29" s="99"/>
+      <c r="L29" s="100"/>
     </row>
     <row r="30" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A30" s="77"/>
-      <c r="B30" s="111" t="s">
+      <c r="A30" s="75"/>
+      <c r="B30" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="111"/>
-      <c r="D30" s="112"/>
-      <c r="E30" s="111"/>
-      <c r="F30" s="76" t="s">
+      <c r="C30" s="109"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="101"/>
-      <c r="K30" s="101"/>
-      <c r="L30" s="102"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="99"/>
+      <c r="K30" s="99"/>
+      <c r="L30" s="100"/>
     </row>
     <row r="31" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A31" s="77"/>
-      <c r="B31" s="111" t="s">
+      <c r="A31" s="75"/>
+      <c r="B31" s="109" t="s">
         <v>188</v>
       </c>
-      <c r="C31" s="111"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="101"/>
-      <c r="K31" s="101"/>
-      <c r="L31" s="102"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="79"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="99"/>
+      <c r="L31" s="100"/>
     </row>
     <row r="32" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A32" s="77"/>
-      <c r="B32" s="89" t="s">
+      <c r="A32" s="75"/>
+      <c r="B32" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="89"/>
+      <c r="C32" s="87"/>
       <c r="D32" s="65"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="76" t="s">
+      <c r="E32" s="87"/>
+      <c r="F32" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="101"/>
-      <c r="K32" s="101"/>
-      <c r="L32" s="102"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="99"/>
+      <c r="K32" s="99"/>
+      <c r="L32" s="100"/>
     </row>
     <row r="33" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A33" s="77"/>
-      <c r="B33" s="89" t="s">
+      <c r="A33" s="75"/>
+      <c r="B33" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="89"/>
+      <c r="C33" s="87"/>
       <c r="D33" s="65"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="76" t="s">
+      <c r="E33" s="87"/>
+      <c r="F33" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="101"/>
-      <c r="K33" s="101"/>
-      <c r="L33" s="102"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="99"/>
+      <c r="K33" s="99"/>
+      <c r="L33" s="100"/>
     </row>
     <row r="34" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A34" s="77"/>
-      <c r="B34" s="89" t="s">
+      <c r="A34" s="75"/>
+      <c r="B34" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="89"/>
+      <c r="C34" s="87"/>
       <c r="D34" s="65"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="76" t="s">
+      <c r="E34" s="87"/>
+      <c r="F34" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="81"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="101"/>
-      <c r="K34" s="101"/>
-      <c r="L34" s="102"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="99"/>
+      <c r="K34" s="99"/>
+      <c r="L34" s="100"/>
     </row>
     <row r="35" spans="1:12" ht="21.95" customHeight="1">
-      <c r="A35" s="77"/>
-      <c r="B35" s="89" t="s">
+      <c r="A35" s="75"/>
+      <c r="B35" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="89"/>
+      <c r="C35" s="87"/>
       <c r="D35" s="65"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="76" t="s">
+      <c r="E35" s="87"/>
+      <c r="F35" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G35" s="81"/>
-      <c r="H35" s="81"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="101"/>
-      <c r="K35" s="101"/>
-      <c r="L35" s="102"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="99"/>
+      <c r="K35" s="99"/>
+      <c r="L35" s="100"/>
     </row>
     <row r="36" spans="1:12" ht="27" customHeight="1">
-      <c r="A36" s="85" t="s">
+      <c r="A36" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="86"/>
-      <c r="C36" s="87"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="85"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
       <c r="I36" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="J36" s="115"/>
-      <c r="K36" s="116"/>
-      <c r="L36" s="117"/>
+      <c r="J36" s="113"/>
+      <c r="K36" s="114"/>
+      <c r="L36" s="115"/>
     </row>
     <row r="37" spans="1:12" ht="16.5" customHeight="1">
       <c r="B37" s="56"/>
@@ -4592,11 +4605,11 @@
       <c r="G37" s="56"/>
       <c r="H37" s="56"/>
       <c r="I37" s="57"/>
-      <c r="J37" s="113" t="s">
+      <c r="J37" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="K37" s="114"/>
-      <c r="L37" s="114"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="112"/>
     </row>
     <row r="39" spans="1:12" ht="18" customHeight="1"/>
   </sheetData>
@@ -4749,20 +4762,20 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1">
-      <c r="A2" s="190" t="s">
+      <c r="A2" s="188" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
+      <c r="B2" s="189"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="189"/>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
       <c r="J2" s="33"/>
-      <c r="K2" s="194"/>
-      <c r="L2" s="192"/>
+      <c r="K2" s="192"/>
+      <c r="L2" s="190"/>
     </row>
     <row r="3" spans="1:12" ht="10.9" customHeight="1">
       <c r="A3" s="33"/>
@@ -4775,8 +4788,8 @@
       <c r="H3" s="33"/>
       <c r="I3" s="33"/>
       <c r="J3" s="33"/>
-      <c r="K3" s="194"/>
-      <c r="L3" s="193"/>
+      <c r="K3" s="192"/>
+      <c r="L3" s="191"/>
     </row>
     <row r="4" spans="1:12" ht="10.9" customHeight="1">
       <c r="A4" s="33"/>
@@ -4806,30 +4819,30 @@
       <c r="G5" s="137"/>
       <c r="H5" s="137"/>
       <c r="I5" s="137"/>
-      <c r="J5" s="195" t="s">
+      <c r="J5" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="196"/>
-      <c r="L5" s="196"/>
+      <c r="K5" s="194"/>
+      <c r="L5" s="194"/>
     </row>
     <row r="6" spans="1:12" ht="24.75" customHeight="1">
       <c r="A6" s="146" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="160" t="s">
+      <c r="B6" s="172" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="160"/>
-      <c r="D6" s="160"/>
-      <c r="E6" s="160"/>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
       <c r="F6" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="161"/>
-      <c r="H6" s="189" t="s">
+      <c r="G6" s="157"/>
+      <c r="H6" s="187" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="163"/>
+      <c r="I6" s="159"/>
       <c r="J6" s="130" t="s">
         <v>10</v>
       </c>
@@ -4838,75 +4851,75 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="146"/>
-      <c r="B7" s="160" t="s">
+      <c r="B7" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
+      <c r="C7" s="172"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="172"/>
       <c r="F7" s="133">
         <v>20240625</v>
       </c>
       <c r="G7" s="139"/>
       <c r="H7" s="139"/>
-      <c r="I7" s="180"/>
-      <c r="J7" s="177" t="s">
+      <c r="I7" s="173"/>
+      <c r="J7" s="184" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="178"/>
-      <c r="L7" s="179"/>
+      <c r="K7" s="185"/>
+      <c r="L7" s="186"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="146"/>
-      <c r="B8" s="160" t="s">
+      <c r="B8" s="172" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="160"/>
-      <c r="D8" s="160"/>
-      <c r="E8" s="160"/>
+      <c r="C8" s="172"/>
+      <c r="D8" s="172"/>
+      <c r="E8" s="172"/>
       <c r="F8" s="133" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="139"/>
       <c r="H8" s="139"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="177" t="s">
+      <c r="I8" s="173"/>
+      <c r="J8" s="184" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="178"/>
-      <c r="L8" s="179"/>
+      <c r="K8" s="185"/>
+      <c r="L8" s="186"/>
     </row>
     <row r="9" spans="1:12" ht="24.75" customHeight="1">
       <c r="A9" s="146"/>
-      <c r="B9" s="160" t="s">
+      <c r="B9" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="160"/>
-      <c r="D9" s="160"/>
-      <c r="E9" s="160"/>
+      <c r="C9" s="172"/>
+      <c r="D9" s="172"/>
+      <c r="E9" s="172"/>
       <c r="F9" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="161"/>
-      <c r="H9" s="162" t="str">
+      <c r="G9" s="157"/>
+      <c r="H9" s="158" t="str">
         <f>"*"&amp;"1"&amp;F9&amp;"*"</f>
         <v>*1S624F25L012*</v>
       </c>
-      <c r="I9" s="163"/>
-      <c r="J9" s="177" t="s">
+      <c r="I9" s="159"/>
+      <c r="J9" s="184" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="178"/>
-      <c r="L9" s="179"/>
+      <c r="K9" s="185"/>
+      <c r="L9" s="186"/>
     </row>
     <row r="10" spans="1:12" ht="17.25" customHeight="1">
       <c r="A10" s="146"/>
-      <c r="B10" s="160" t="s">
+      <c r="B10" s="172" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
+      <c r="C10" s="172"/>
+      <c r="D10" s="172"/>
+      <c r="E10" s="172"/>
       <c r="F10" s="133">
         <v>4</v>
       </c>
@@ -4915,20 +4928,20 @@
       <c r="I10" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="177" t="s">
+      <c r="J10" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="178"/>
-      <c r="L10" s="179"/>
+      <c r="K10" s="185"/>
+      <c r="L10" s="186"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="146"/>
-      <c r="B11" s="160" t="s">
+      <c r="B11" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="160"/>
-      <c r="D11" s="160"/>
-      <c r="E11" s="160"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="172"/>
       <c r="F11" s="133">
         <v>10972</v>
       </c>
@@ -4937,35 +4950,35 @@
       <c r="I11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="177" t="s">
+      <c r="J11" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="K11" s="178"/>
-      <c r="L11" s="179"/>
+      <c r="K11" s="185"/>
+      <c r="L11" s="186"/>
     </row>
     <row r="12" spans="1:12" ht="24" customHeight="1">
       <c r="A12" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="160" t="s">
+      <c r="B12" s="172" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="160"/>
-      <c r="D12" s="160"/>
-      <c r="E12" s="160"/>
+      <c r="C12" s="172"/>
+      <c r="D12" s="172"/>
+      <c r="E12" s="172"/>
       <c r="F12" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="161"/>
-      <c r="H12" s="164" t="s">
+      <c r="G12" s="157"/>
+      <c r="H12" s="160" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="163"/>
-      <c r="J12" s="177" t="s">
+      <c r="I12" s="159"/>
+      <c r="J12" s="184" t="s">
         <v>29</v>
       </c>
-      <c r="K12" s="178"/>
-      <c r="L12" s="179"/>
+      <c r="K12" s="185"/>
+      <c r="L12" s="186"/>
     </row>
     <row r="13" spans="1:12" ht="16.899999999999999" customHeight="1">
       <c r="A13" s="146"/>
@@ -4978,16 +4991,16 @@
       <c r="F13" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="157"/>
-      <c r="H13" s="158">
+      <c r="G13" s="171"/>
+      <c r="H13" s="182">
         <v>1.841</v>
       </c>
-      <c r="I13" s="159"/>
-      <c r="J13" s="177" t="s">
+      <c r="I13" s="183"/>
+      <c r="J13" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="178"/>
-      <c r="L13" s="179"/>
+      <c r="K13" s="185"/>
+      <c r="L13" s="186"/>
     </row>
     <row r="14" spans="1:12" ht="16.899999999999999" customHeight="1">
       <c r="A14" s="146"/>
@@ -5008,11 +5021,11 @@
       <c r="I14" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="J14" s="177" t="s">
+      <c r="J14" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="178"/>
-      <c r="L14" s="179"/>
+      <c r="K14" s="185"/>
+      <c r="L14" s="186"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="140" t="s">
@@ -5023,29 +5036,29 @@
       <c r="D15" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="186"/>
-      <c r="F15" s="187"/>
-      <c r="G15" s="186"/>
-      <c r="H15" s="188"/>
+      <c r="E15" s="168"/>
+      <c r="F15" s="169"/>
+      <c r="G15" s="168"/>
+      <c r="H15" s="170"/>
       <c r="I15" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="J15" s="177" t="s">
+      <c r="J15" s="184" t="s">
         <v>38</v>
       </c>
-      <c r="K15" s="178"/>
-      <c r="L15" s="179"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="186"/>
     </row>
     <row r="16" spans="1:12" ht="19.5" customHeight="1">
       <c r="A16" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="181" t="s">
+      <c r="B16" s="163" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="182"/>
+      <c r="C16" s="164"/>
       <c r="D16" s="137"/>
-      <c r="E16" s="183"/>
+      <c r="E16" s="165"/>
       <c r="F16" s="32">
         <v>22.1</v>
       </c>
@@ -5058,9 +5071,9 @@
       <c r="I16" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="J16" s="177"/>
-      <c r="K16" s="178"/>
-      <c r="L16" s="179"/>
+      <c r="J16" s="184"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="186"/>
     </row>
     <row r="17" spans="1:12" ht="18.75" hidden="1" customHeight="1">
       <c r="A17" s="146"/>
@@ -5073,12 +5086,12 @@
       <c r="F17" s="136" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="184"/>
-      <c r="H17" s="184"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="177"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="179"/>
+      <c r="G17" s="166"/>
+      <c r="H17" s="166"/>
+      <c r="I17" s="167"/>
+      <c r="J17" s="184"/>
+      <c r="K17" s="185"/>
+      <c r="L17" s="186"/>
     </row>
     <row r="18" spans="1:12" ht="24" customHeight="1">
       <c r="A18" s="146"/>
@@ -5087,16 +5100,16 @@
       </c>
       <c r="C18" s="144"/>
       <c r="D18" s="137"/>
-      <c r="E18" s="165"/>
+      <c r="E18" s="161"/>
       <c r="F18" s="133" t="s">
         <v>44</v>
       </c>
       <c r="G18" s="139"/>
       <c r="H18" s="136"/>
       <c r="I18" s="139"/>
-      <c r="J18" s="178"/>
-      <c r="K18" s="178"/>
-      <c r="L18" s="179"/>
+      <c r="J18" s="185"/>
+      <c r="K18" s="185"/>
+      <c r="L18" s="186"/>
     </row>
     <row r="19" spans="1:12" ht="32.25" customHeight="1">
       <c r="A19" s="146"/>
@@ -5105,16 +5118,16 @@
       </c>
       <c r="C19" s="144"/>
       <c r="D19" s="137"/>
-      <c r="E19" s="165"/>
+      <c r="E19" s="161"/>
       <c r="F19" s="136" t="s">
         <v>44</v>
       </c>
       <c r="G19" s="139"/>
       <c r="H19" s="139"/>
       <c r="I19" s="139"/>
-      <c r="J19" s="178"/>
-      <c r="K19" s="178"/>
-      <c r="L19" s="179"/>
+      <c r="J19" s="185"/>
+      <c r="K19" s="185"/>
+      <c r="L19" s="186"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="146"/>
@@ -5123,18 +5136,18 @@
       </c>
       <c r="C20" s="144"/>
       <c r="D20" s="137"/>
-      <c r="E20" s="165"/>
+      <c r="E20" s="161"/>
       <c r="F20" s="133" t="s">
         <v>44</v>
       </c>
       <c r="G20" s="139"/>
       <c r="H20" s="139"/>
       <c r="I20" s="139"/>
-      <c r="J20" s="198" t="s">
+      <c r="J20" s="196" t="s">
         <v>48</v>
       </c>
-      <c r="K20" s="199"/>
-      <c r="L20" s="200"/>
+      <c r="K20" s="197"/>
+      <c r="L20" s="198"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="146"/>
@@ -5143,18 +5156,18 @@
       </c>
       <c r="C21" s="144"/>
       <c r="D21" s="137"/>
-      <c r="E21" s="165"/>
+      <c r="E21" s="161"/>
       <c r="F21" s="133" t="s">
         <v>44</v>
       </c>
       <c r="G21" s="139"/>
       <c r="H21" s="139"/>
       <c r="I21" s="139"/>
-      <c r="J21" s="198" t="s">
+      <c r="J21" s="196" t="s">
         <v>50</v>
       </c>
-      <c r="K21" s="199"/>
-      <c r="L21" s="200"/>
+      <c r="K21" s="197"/>
+      <c r="L21" s="198"/>
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1">
       <c r="A22" s="146"/>
@@ -5167,19 +5180,19 @@
       <c r="F22" s="133">
         <v>10690</v>
       </c>
-      <c r="G22" s="166"/>
-      <c r="H22" s="166"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="162"/>
       <c r="I22" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="J22" s="198" t="s">
+      <c r="J22" s="196" t="s">
         <v>52</v>
       </c>
-      <c r="K22" s="199"/>
-      <c r="L22" s="200"/>
+      <c r="K22" s="197"/>
+      <c r="L22" s="198"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A23" s="175" t="s">
+      <c r="A23" s="128" t="s">
         <v>53</v>
       </c>
       <c r="B23" s="37" t="s">
@@ -5198,14 +5211,14 @@
       <c r="I23" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="J23" s="198" t="s">
+      <c r="J23" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="K23" s="199"/>
-      <c r="L23" s="200"/>
+      <c r="K23" s="197"/>
+      <c r="L23" s="198"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="176"/>
+      <c r="A24" s="129"/>
       <c r="B24" s="138" t="s">
         <v>58</v>
       </c>
@@ -5220,11 +5233,11 @@
       <c r="I24" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="198" t="s">
+      <c r="J24" s="196" t="s">
         <v>59</v>
       </c>
-      <c r="K24" s="199"/>
-      <c r="L24" s="200"/>
+      <c r="K24" s="197"/>
+      <c r="L24" s="198"/>
     </row>
     <row r="25" spans="1:12" ht="17.25" customHeight="1">
       <c r="A25" s="145" t="s">
@@ -5249,8 +5262,8 @@
       <c r="J25" s="137" t="s">
         <v>63</v>
       </c>
-      <c r="K25" s="194"/>
-      <c r="L25" s="194"/>
+      <c r="K25" s="192"/>
+      <c r="L25" s="192"/>
     </row>
     <row r="26" spans="1:12" ht="18" customHeight="1">
       <c r="A26" s="146"/>
@@ -5272,9 +5285,9 @@
       <c r="I26" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="J26" s="171"/>
-      <c r="K26" s="168"/>
-      <c r="L26" s="169"/>
+      <c r="J26" s="178"/>
+      <c r="K26" s="175"/>
+      <c r="L26" s="176"/>
     </row>
     <row r="27" spans="1:12" ht="18" customHeight="1">
       <c r="A27" s="146"/>
@@ -5292,9 +5305,9 @@
       <c r="I27" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="J27" s="171"/>
-      <c r="K27" s="168"/>
-      <c r="L27" s="169"/>
+      <c r="J27" s="178"/>
+      <c r="K27" s="175"/>
+      <c r="L27" s="176"/>
     </row>
     <row r="28" spans="1:12" ht="18" customHeight="1">
       <c r="A28" s="146"/>
@@ -5310,9 +5323,9 @@
       <c r="G28" s="139"/>
       <c r="H28" s="139"/>
       <c r="I28" s="139"/>
-      <c r="J28" s="171"/>
-      <c r="K28" s="171"/>
-      <c r="L28" s="197"/>
+      <c r="J28" s="178"/>
+      <c r="K28" s="178"/>
+      <c r="L28" s="195"/>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1">
       <c r="A29" s="146"/>
@@ -5328,9 +5341,9 @@
       <c r="G29" s="139"/>
       <c r="H29" s="139"/>
       <c r="I29" s="139"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="167"/>
-      <c r="L29" s="172"/>
+      <c r="J29" s="178"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="179"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1">
       <c r="A30" s="146"/>
@@ -5346,9 +5359,9 @@
       <c r="G30" s="139"/>
       <c r="H30" s="139"/>
       <c r="I30" s="139"/>
-      <c r="J30" s="167"/>
-      <c r="K30" s="168"/>
-      <c r="L30" s="169"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="175"/>
+      <c r="L30" s="176"/>
     </row>
     <row r="31" spans="1:12" ht="16.5" customHeight="1">
       <c r="A31" s="146"/>
@@ -5362,9 +5375,9 @@
       <c r="G31" s="139"/>
       <c r="H31" s="139"/>
       <c r="I31" s="139"/>
-      <c r="J31" s="167"/>
-      <c r="K31" s="168"/>
-      <c r="L31" s="169"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="175"/>
+      <c r="L31" s="176"/>
     </row>
     <row r="32" spans="1:12" ht="18" customHeight="1">
       <c r="A32" s="146"/>
@@ -5380,9 +5393,9 @@
       <c r="G32" s="139"/>
       <c r="H32" s="139"/>
       <c r="I32" s="139"/>
-      <c r="J32" s="167"/>
-      <c r="K32" s="168"/>
-      <c r="L32" s="169"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="175"/>
+      <c r="L32" s="176"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="146"/>
@@ -5398,9 +5411,9 @@
       <c r="G33" s="139"/>
       <c r="H33" s="139"/>
       <c r="I33" s="139"/>
-      <c r="J33" s="167"/>
-      <c r="K33" s="168"/>
-      <c r="L33" s="169"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="175"/>
+      <c r="L33" s="176"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="146"/>
@@ -5416,9 +5429,9 @@
       <c r="G34" s="139"/>
       <c r="H34" s="139"/>
       <c r="I34" s="139"/>
-      <c r="J34" s="167"/>
-      <c r="K34" s="168"/>
-      <c r="L34" s="169"/>
+      <c r="J34" s="174"/>
+      <c r="K34" s="175"/>
+      <c r="L34" s="176"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="146"/>
@@ -5434,9 +5447,9 @@
       <c r="G35" s="139"/>
       <c r="H35" s="139"/>
       <c r="I35" s="139"/>
-      <c r="J35" s="167"/>
-      <c r="K35" s="168"/>
-      <c r="L35" s="169"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="175"/>
+      <c r="L35" s="176"/>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="140" t="s">
@@ -5455,8 +5468,8 @@
         <v>37</v>
       </c>
       <c r="J36" s="148"/>
-      <c r="K36" s="173"/>
-      <c r="L36" s="174"/>
+      <c r="K36" s="180"/>
+      <c r="L36" s="181"/>
     </row>
     <row r="37" spans="1:12" ht="16.5" customHeight="1">
       <c r="A37" s="33"/>
@@ -5467,11 +5480,11 @@
       <c r="G37" s="40"/>
       <c r="H37" s="40"/>
       <c r="I37" s="42"/>
-      <c r="J37" s="170" t="s">
+      <c r="J37" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="K37" s="168"/>
-      <c r="L37" s="168"/>
+      <c r="K37" s="175"/>
+      <c r="L37" s="175"/>
     </row>
     <row r="38" spans="1:12">
       <c r="D38" s="32"/>
@@ -5486,7 +5499,6 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="104">
-    <mergeCell ref="J17:L17"/>
     <mergeCell ref="J18:L18"/>
     <mergeCell ref="J19:L19"/>
     <mergeCell ref="J25:L25"/>
@@ -5498,8 +5510,6 @@
     <mergeCell ref="J22:L22"/>
     <mergeCell ref="J23:L23"/>
     <mergeCell ref="J24:L24"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J11:L11"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J12:L12"/>
     <mergeCell ref="J13:L13"/>
@@ -5510,7 +5520,6 @@
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J15:L15"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -5535,6 +5544,17 @@
     <mergeCell ref="J33:L33"/>
     <mergeCell ref="J36:L36"/>
     <mergeCell ref="J32:L32"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:I31"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J17:L17"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="H9:I9"/>
@@ -5555,16 +5575,10 @@
     <mergeCell ref="F18:I18"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:I31"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B33:E33"/>
     <mergeCell ref="A16:A22"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="B13:E14"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B12:E12"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="F23:H23"/>
@@ -5589,7 +5603,6 @@
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="F28:I28"/>
     <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:I29"/>
   </mergeCells>
   <phoneticPr fontId="34" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -5624,221 +5637,221 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="31.5" customHeight="1">
-      <c r="A2" s="201" t="s">
+      <c r="A2" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="J2" s="158"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="J2" s="182"/>
       <c r="K2" s="143"/>
-      <c r="L2" s="202"/>
+      <c r="L2" s="200"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="J3" s="158"/>
+      <c r="J3" s="182"/>
       <c r="K3" s="143"/>
-      <c r="L3" s="203"/>
+      <c r="L3" s="201"/>
     </row>
     <row r="4" spans="1:12" ht="17.25" customHeight="1"/>
     <row r="5" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A5" s="217" t="s">
+      <c r="A5" s="215" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="218"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="218"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="220" t="s">
+      <c r="B5" s="216"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="218" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="218"/>
-      <c r="H5" s="218"/>
-      <c r="I5" s="221"/>
-      <c r="J5" s="222" t="s">
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="220" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="223"/>
-      <c r="L5" s="224"/>
+      <c r="K5" s="221"/>
+      <c r="L5" s="222"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="225" t="s">
+      <c r="A6" s="223" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="212" t="s">
+      <c r="B6" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="213"/>
-      <c r="D6" s="213"/>
-      <c r="E6" s="214"/>
-      <c r="F6" s="207" t="s">
+      <c r="C6" s="211"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="212"/>
+      <c r="F6" s="205" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="208"/>
-      <c r="H6" s="208"/>
-      <c r="I6" s="209"/>
-      <c r="J6" s="210"/>
-      <c r="K6" s="158"/>
-      <c r="L6" s="211"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="207"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="182"/>
+      <c r="L6" s="209"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="226"/>
-      <c r="B7" s="212" t="s">
+      <c r="A7" s="224"/>
+      <c r="B7" s="210" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="213"/>
-      <c r="D7" s="213"/>
-      <c r="E7" s="214"/>
-      <c r="F7" s="207" t="s">
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="212"/>
+      <c r="F7" s="205" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="208"/>
-      <c r="H7" s="208"/>
-      <c r="I7" s="209"/>
-      <c r="J7" s="210"/>
-      <c r="K7" s="158"/>
-      <c r="L7" s="211"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="206"/>
+      <c r="I7" s="207"/>
+      <c r="J7" s="208"/>
+      <c r="K7" s="182"/>
+      <c r="L7" s="209"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="226"/>
-      <c r="B8" s="212" t="s">
+      <c r="A8" s="224"/>
+      <c r="B8" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="213"/>
-      <c r="D8" s="213"/>
-      <c r="E8" s="214"/>
-      <c r="F8" s="207" t="s">
+      <c r="C8" s="211"/>
+      <c r="D8" s="211"/>
+      <c r="E8" s="212"/>
+      <c r="F8" s="205" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="208"/>
-      <c r="H8" s="208"/>
-      <c r="I8" s="209"/>
-      <c r="J8" s="210"/>
-      <c r="K8" s="158"/>
-      <c r="L8" s="211"/>
+      <c r="G8" s="206"/>
+      <c r="H8" s="206"/>
+      <c r="I8" s="207"/>
+      <c r="J8" s="208"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="209"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="226"/>
-      <c r="B9" s="204" t="s">
+      <c r="A9" s="224"/>
+      <c r="B9" s="202" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="205"/>
-      <c r="D9" s="205"/>
-      <c r="E9" s="206"/>
-      <c r="F9" s="207" t="s">
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="204"/>
+      <c r="F9" s="205" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
-      <c r="I9" s="209"/>
-      <c r="J9" s="210"/>
-      <c r="K9" s="158"/>
-      <c r="L9" s="211"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="207"/>
+      <c r="J9" s="208"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="209"/>
     </row>
     <row r="10" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A10" s="226"/>
-      <c r="B10" s="212" t="s">
+      <c r="A10" s="224"/>
+      <c r="B10" s="210" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="213"/>
-      <c r="D10" s="213"/>
-      <c r="E10" s="214"/>
-      <c r="F10" s="215" t="s">
+      <c r="C10" s="211"/>
+      <c r="D10" s="211"/>
+      <c r="E10" s="212"/>
+      <c r="F10" s="213" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="216"/>
-      <c r="H10" s="216"/>
+      <c r="G10" s="214"/>
+      <c r="H10" s="214"/>
       <c r="I10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="210"/>
-      <c r="K10" s="158"/>
-      <c r="L10" s="211"/>
+      <c r="J10" s="208"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="209"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="227"/>
-      <c r="B11" s="212" t="s">
+      <c r="A11" s="225"/>
+      <c r="B11" s="210" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="213"/>
-      <c r="D11" s="213"/>
-      <c r="E11" s="214"/>
-      <c r="F11" s="233" t="s">
+      <c r="C11" s="211"/>
+      <c r="D11" s="211"/>
+      <c r="E11" s="212"/>
+      <c r="F11" s="231" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="234"/>
-      <c r="H11" s="234"/>
+      <c r="G11" s="232"/>
+      <c r="H11" s="232"/>
       <c r="I11" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="J11" s="210"/>
-      <c r="K11" s="158"/>
-      <c r="L11" s="211"/>
+      <c r="J11" s="208"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="209"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="225" t="s">
+      <c r="A12" s="223" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="204" t="s">
+      <c r="B12" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="205"/>
-      <c r="D12" s="205"/>
-      <c r="E12" s="206"/>
-      <c r="F12" s="207" t="s">
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="204"/>
+      <c r="F12" s="205" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="208"/>
-      <c r="H12" s="208"/>
-      <c r="I12" s="209"/>
-      <c r="J12" s="210"/>
-      <c r="K12" s="158"/>
-      <c r="L12" s="211"/>
+      <c r="G12" s="206"/>
+      <c r="H12" s="206"/>
+      <c r="I12" s="207"/>
+      <c r="J12" s="208"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="209"/>
     </row>
     <row r="13" spans="1:12" ht="18.75" hidden="1" customHeight="1">
-      <c r="A13" s="226"/>
-      <c r="B13" s="228" t="s">
+      <c r="A13" s="224"/>
+      <c r="B13" s="226" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="229"/>
-      <c r="D13" s="229"/>
-      <c r="E13" s="230"/>
-      <c r="F13" s="207" t="s">
+      <c r="C13" s="227"/>
+      <c r="D13" s="227"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="205" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="231"/>
-      <c r="H13" s="231"/>
-      <c r="I13" s="232"/>
-      <c r="J13" s="210"/>
-      <c r="K13" s="158"/>
-      <c r="L13" s="211"/>
+      <c r="G13" s="229"/>
+      <c r="H13" s="229"/>
+      <c r="I13" s="230"/>
+      <c r="J13" s="208"/>
+      <c r="K13" s="182"/>
+      <c r="L13" s="209"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="226"/>
-      <c r="B14" s="235" t="s">
+      <c r="A14" s="224"/>
+      <c r="B14" s="233" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="236"/>
-      <c r="D14" s="236"/>
-      <c r="E14" s="237"/>
-      <c r="F14" s="241" t="s">
+      <c r="C14" s="234"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="239" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="242"/>
+      <c r="G14" s="240"/>
       <c r="H14" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="243"/>
-      <c r="K14" s="158"/>
-      <c r="L14" s="211"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="182"/>
+      <c r="L14" s="209"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="227"/>
-      <c r="B15" s="238"/>
-      <c r="C15" s="239"/>
-      <c r="D15" s="239"/>
-      <c r="E15" s="240"/>
+      <c r="A15" s="225"/>
+      <c r="B15" s="236"/>
+      <c r="C15" s="237"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="238"/>
       <c r="F15" s="9" t="s">
         <v>93</v>
       </c>
@@ -5851,68 +5864,68 @@
       <c r="I15" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="J15" s="243"/>
-      <c r="K15" s="158"/>
-      <c r="L15" s="211"/>
+      <c r="J15" s="241"/>
+      <c r="K15" s="182"/>
+      <c r="L15" s="209"/>
     </row>
     <row r="16" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A16" s="244" t="s">
+      <c r="A16" s="242" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="245"/>
-      <c r="C16" s="246"/>
-      <c r="D16" s="247" t="s">
+      <c r="B16" s="243"/>
+      <c r="C16" s="244"/>
+      <c r="D16" s="245" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="248"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="248"/>
-      <c r="H16" s="248"/>
+      <c r="E16" s="246"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
       <c r="I16" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="210"/>
-      <c r="K16" s="158"/>
-      <c r="L16" s="211"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="182"/>
+      <c r="L16" s="209"/>
     </row>
     <row r="17" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A17" s="255" t="s">
+      <c r="A17" s="253" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="249" t="s">
+      <c r="B17" s="247" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="250"/>
-      <c r="D17" s="250"/>
-      <c r="E17" s="251"/>
+      <c r="C17" s="248"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="249"/>
       <c r="F17" s="13" t="s">
         <v>97</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="6"/>
-      <c r="J17" s="210"/>
-      <c r="K17" s="158"/>
-      <c r="L17" s="211"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="182"/>
+      <c r="L17" s="209"/>
     </row>
     <row r="18" spans="1:12" ht="4.5" customHeight="1">
-      <c r="A18" s="226"/>
-      <c r="B18" s="252"/>
-      <c r="C18" s="253"/>
-      <c r="D18" s="253"/>
-      <c r="E18" s="254"/>
+      <c r="A18" s="224"/>
+      <c r="B18" s="250"/>
+      <c r="C18" s="251"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="252"/>
       <c r="F18" s="14"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="210"/>
-      <c r="K18" s="158"/>
-      <c r="L18" s="211"/>
+      <c r="J18" s="208"/>
+      <c r="K18" s="182"/>
+      <c r="L18" s="209"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="226"/>
-      <c r="B19" s="238"/>
-      <c r="C19" s="239"/>
-      <c r="D19" s="239"/>
-      <c r="E19" s="240"/>
+      <c r="A19" s="224"/>
+      <c r="B19" s="236"/>
+      <c r="C19" s="237"/>
+      <c r="D19" s="237"/>
+      <c r="E19" s="238"/>
       <c r="F19" s="15" t="s">
         <v>98</v>
       </c>
@@ -5923,146 +5936,146 @@
       <c r="I19" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="J19" s="210"/>
-      <c r="K19" s="158"/>
-      <c r="L19" s="211"/>
+      <c r="J19" s="208"/>
+      <c r="K19" s="182"/>
+      <c r="L19" s="209"/>
     </row>
     <row r="20" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A20" s="226"/>
-      <c r="B20" s="256" t="s">
+      <c r="A20" s="224"/>
+      <c r="B20" s="254" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="257"/>
-      <c r="D20" s="257"/>
-      <c r="E20" s="258"/>
-      <c r="F20" s="259" t="s">
+      <c r="C20" s="255"/>
+      <c r="D20" s="255"/>
+      <c r="E20" s="256"/>
+      <c r="F20" s="257" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="260"/>
-      <c r="H20" s="260"/>
-      <c r="I20" s="261"/>
-      <c r="J20" s="210"/>
-      <c r="K20" s="158"/>
-      <c r="L20" s="211"/>
+      <c r="G20" s="258"/>
+      <c r="H20" s="258"/>
+      <c r="I20" s="259"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="182"/>
+      <c r="L20" s="209"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="226"/>
-      <c r="B21" s="256" t="s">
+      <c r="A21" s="224"/>
+      <c r="B21" s="254" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="257"/>
-      <c r="D21" s="257"/>
-      <c r="E21" s="258"/>
-      <c r="F21" s="259" t="s">
+      <c r="C21" s="255"/>
+      <c r="D21" s="255"/>
+      <c r="E21" s="256"/>
+      <c r="F21" s="257" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="262"/>
-      <c r="H21" s="262"/>
-      <c r="I21" s="263"/>
-      <c r="J21" s="243"/>
-      <c r="K21" s="158"/>
-      <c r="L21" s="211"/>
+      <c r="G21" s="260"/>
+      <c r="H21" s="260"/>
+      <c r="I21" s="261"/>
+      <c r="J21" s="241"/>
+      <c r="K21" s="182"/>
+      <c r="L21" s="209"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="226"/>
-      <c r="B22" s="256" t="s">
+      <c r="A22" s="224"/>
+      <c r="B22" s="254" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="257"/>
-      <c r="D22" s="257"/>
-      <c r="E22" s="258"/>
-      <c r="F22" s="259" t="s">
+      <c r="C22" s="255"/>
+      <c r="D22" s="255"/>
+      <c r="E22" s="256"/>
+      <c r="F22" s="257" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="260"/>
-      <c r="H22" s="260"/>
-      <c r="I22" s="261"/>
-      <c r="J22" s="243"/>
-      <c r="K22" s="158"/>
-      <c r="L22" s="211"/>
+      <c r="G22" s="258"/>
+      <c r="H22" s="258"/>
+      <c r="I22" s="259"/>
+      <c r="J22" s="241"/>
+      <c r="K22" s="182"/>
+      <c r="L22" s="209"/>
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1">
-      <c r="A23" s="226"/>
-      <c r="B23" s="235" t="s">
+      <c r="A23" s="224"/>
+      <c r="B23" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="236"/>
-      <c r="D23" s="236"/>
-      <c r="E23" s="237"/>
-      <c r="F23" s="267" t="s">
+      <c r="C23" s="234"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="235"/>
+      <c r="F23" s="265" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="268"/>
-      <c r="H23" s="268"/>
-      <c r="I23" s="269"/>
-      <c r="J23" s="243"/>
-      <c r="K23" s="158"/>
-      <c r="L23" s="211"/>
+      <c r="G23" s="266"/>
+      <c r="H23" s="266"/>
+      <c r="I23" s="267"/>
+      <c r="J23" s="241"/>
+      <c r="K23" s="182"/>
+      <c r="L23" s="209"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="226"/>
-      <c r="B24" s="273" t="s">
+      <c r="A24" s="224"/>
+      <c r="B24" s="271" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="274"/>
-      <c r="D24" s="274"/>
-      <c r="E24" s="275"/>
-      <c r="F24" s="270"/>
-      <c r="G24" s="271"/>
-      <c r="H24" s="271"/>
-      <c r="I24" s="272"/>
-      <c r="J24" s="243"/>
-      <c r="K24" s="158"/>
-      <c r="L24" s="211"/>
+      <c r="C24" s="272"/>
+      <c r="D24" s="272"/>
+      <c r="E24" s="273"/>
+      <c r="F24" s="268"/>
+      <c r="G24" s="269"/>
+      <c r="H24" s="269"/>
+      <c r="I24" s="270"/>
+      <c r="J24" s="241"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="209"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="227"/>
-      <c r="B25" s="264" t="s">
+      <c r="A25" s="225"/>
+      <c r="B25" s="262" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="265"/>
-      <c r="D25" s="265"/>
-      <c r="E25" s="266"/>
-      <c r="F25" s="259" t="s">
+      <c r="C25" s="263"/>
+      <c r="D25" s="263"/>
+      <c r="E25" s="264"/>
+      <c r="F25" s="257" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="260"/>
-      <c r="H25" s="260"/>
-      <c r="I25" s="261"/>
-      <c r="J25" s="243"/>
-      <c r="K25" s="158"/>
-      <c r="L25" s="211"/>
+      <c r="G25" s="258"/>
+      <c r="H25" s="258"/>
+      <c r="I25" s="259"/>
+      <c r="J25" s="241"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="209"/>
     </row>
     <row r="26" spans="1:12" ht="17.25" customHeight="1">
-      <c r="A26" s="225" t="s">
+      <c r="A26" s="223" t="s">
         <v>53</v>
       </c>
       <c r="B26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="256" t="s">
+      <c r="C26" s="254" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="257"/>
-      <c r="E26" s="258"/>
-      <c r="F26" s="259" t="s">
+      <c r="D26" s="255"/>
+      <c r="E26" s="256"/>
+      <c r="F26" s="257" t="s">
         <v>112</v>
       </c>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="261"/>
-      <c r="J26" s="243"/>
-      <c r="K26" s="158"/>
-      <c r="L26" s="211"/>
+      <c r="G26" s="258"/>
+      <c r="H26" s="258"/>
+      <c r="I26" s="259"/>
+      <c r="J26" s="241"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="209"/>
     </row>
     <row r="27" spans="1:12" ht="18" customHeight="1">
-      <c r="A27" s="226"/>
-      <c r="B27" s="264" t="s">
+      <c r="A27" s="224"/>
+      <c r="B27" s="262" t="s">
         <v>113</v>
       </c>
-      <c r="C27" s="276"/>
-      <c r="D27" s="216"/>
-      <c r="E27" s="277"/>
+      <c r="C27" s="274"/>
+      <c r="D27" s="214"/>
+      <c r="E27" s="275"/>
       <c r="F27" s="12" t="s">
         <v>114</v>
       </c>
@@ -6073,23 +6086,23 @@
         <v>115</v>
       </c>
       <c r="I27" s="17"/>
-      <c r="J27" s="243"/>
-      <c r="K27" s="158"/>
-      <c r="L27" s="211"/>
+      <c r="J27" s="241"/>
+      <c r="K27" s="182"/>
+      <c r="L27" s="209"/>
     </row>
     <row r="28" spans="1:12" ht="18" customHeight="1">
-      <c r="A28" s="226"/>
-      <c r="B28" s="264" t="s">
+      <c r="A28" s="224"/>
+      <c r="B28" s="262" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="265"/>
-      <c r="D28" s="265"/>
-      <c r="E28" s="266"/>
-      <c r="F28" s="215" t="s">
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="264"/>
+      <c r="F28" s="213" t="s">
         <v>117</v>
       </c>
-      <c r="G28" s="216"/>
-      <c r="H28" s="216"/>
+      <c r="G28" s="214"/>
+      <c r="H28" s="214"/>
       <c r="I28" s="21" t="s">
         <v>118</v>
       </c>
@@ -6097,56 +6110,56 @@
       <c r="L28" s="7"/>
     </row>
     <row r="29" spans="1:12" ht="18" customHeight="1">
-      <c r="A29" s="227"/>
-      <c r="B29" s="264" t="s">
+      <c r="A29" s="225"/>
+      <c r="B29" s="262" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="265"/>
-      <c r="D29" s="265"/>
-      <c r="E29" s="266"/>
-      <c r="F29" s="259">
+      <c r="C29" s="263"/>
+      <c r="D29" s="263"/>
+      <c r="E29" s="264"/>
+      <c r="F29" s="257">
         <v>1</v>
       </c>
-      <c r="G29" s="260"/>
-      <c r="H29" s="260"/>
-      <c r="I29" s="261"/>
-      <c r="J29" s="243"/>
-      <c r="K29" s="158"/>
-      <c r="L29" s="211"/>
+      <c r="G29" s="258"/>
+      <c r="H29" s="258"/>
+      <c r="I29" s="259"/>
+      <c r="J29" s="241"/>
+      <c r="K29" s="182"/>
+      <c r="L29" s="209"/>
     </row>
     <row r="30" spans="1:12" ht="18" customHeight="1">
-      <c r="A30" s="225" t="s">
+      <c r="A30" s="223" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="264" t="s">
+      <c r="B30" s="262" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="265"/>
-      <c r="D30" s="266"/>
+      <c r="C30" s="263"/>
+      <c r="D30" s="264"/>
       <c r="E30" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F30" s="215" t="s">
+      <c r="F30" s="213" t="s">
         <v>121</v>
       </c>
-      <c r="G30" s="216"/>
-      <c r="H30" s="216"/>
+      <c r="G30" s="214"/>
+      <c r="H30" s="214"/>
       <c r="I30" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J30" s="289" t="s">
+      <c r="J30" s="287" t="s">
         <v>63</v>
       </c>
-      <c r="K30" s="290"/>
-      <c r="L30" s="291"/>
+      <c r="K30" s="288"/>
+      <c r="L30" s="289"/>
     </row>
     <row r="31" spans="1:12" ht="18.75" customHeight="1">
-      <c r="A31" s="226"/>
-      <c r="B31" s="264" t="s">
+      <c r="A31" s="224"/>
+      <c r="B31" s="262" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="265"/>
-      <c r="D31" s="266"/>
+      <c r="C31" s="263"/>
+      <c r="D31" s="264"/>
       <c r="E31" s="4" t="s">
         <v>122</v>
       </c>
@@ -6160,171 +6173,171 @@
       <c r="I31" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J31" s="243"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="211"/>
+      <c r="J31" s="241"/>
+      <c r="K31" s="182"/>
+      <c r="L31" s="209"/>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A32" s="226"/>
-      <c r="B32" s="292" t="s">
+      <c r="A32" s="224"/>
+      <c r="B32" s="290" t="s">
         <v>124</v>
       </c>
-      <c r="C32" s="293"/>
-      <c r="D32" s="293"/>
-      <c r="E32" s="294"/>
-      <c r="F32" s="259" t="s">
+      <c r="C32" s="291"/>
+      <c r="D32" s="291"/>
+      <c r="E32" s="292"/>
+      <c r="F32" s="257" t="s">
         <v>125</v>
       </c>
-      <c r="G32" s="260"/>
-      <c r="H32" s="260"/>
-      <c r="I32" s="261"/>
-      <c r="J32" s="243"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="211"/>
+      <c r="G32" s="258"/>
+      <c r="H32" s="258"/>
+      <c r="I32" s="259"/>
+      <c r="J32" s="241"/>
+      <c r="K32" s="182"/>
+      <c r="L32" s="209"/>
     </row>
     <row r="33" spans="1:12" ht="18" customHeight="1">
-      <c r="A33" s="226"/>
-      <c r="B33" s="264" t="s">
+      <c r="A33" s="224"/>
+      <c r="B33" s="262" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="265"/>
-      <c r="D33" s="265"/>
-      <c r="E33" s="266"/>
-      <c r="F33" s="259" t="s">
+      <c r="C33" s="263"/>
+      <c r="D33" s="263"/>
+      <c r="E33" s="264"/>
+      <c r="F33" s="257" t="s">
         <v>126</v>
       </c>
-      <c r="G33" s="260"/>
-      <c r="H33" s="260"/>
-      <c r="I33" s="261"/>
-      <c r="J33" s="243"/>
-      <c r="K33" s="282"/>
-      <c r="L33" s="283"/>
+      <c r="G33" s="258"/>
+      <c r="H33" s="258"/>
+      <c r="I33" s="259"/>
+      <c r="J33" s="241"/>
+      <c r="K33" s="280"/>
+      <c r="L33" s="281"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="226"/>
-      <c r="B34" s="235" t="s">
+      <c r="A34" s="224"/>
+      <c r="B34" s="233" t="s">
         <v>127</v>
       </c>
-      <c r="C34" s="236"/>
-      <c r="D34" s="236"/>
-      <c r="E34" s="237"/>
-      <c r="F34" s="267" t="s">
+      <c r="C34" s="234"/>
+      <c r="D34" s="234"/>
+      <c r="E34" s="235"/>
+      <c r="F34" s="265" t="s">
         <v>128</v>
       </c>
-      <c r="G34" s="284"/>
-      <c r="H34" s="284"/>
-      <c r="I34" s="285"/>
-      <c r="J34" s="243"/>
-      <c r="K34" s="158"/>
-      <c r="L34" s="211"/>
+      <c r="G34" s="282"/>
+      <c r="H34" s="282"/>
+      <c r="I34" s="283"/>
+      <c r="J34" s="241"/>
+      <c r="K34" s="182"/>
+      <c r="L34" s="209"/>
     </row>
     <row r="35" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A35" s="226"/>
-      <c r="B35" s="273" t="s">
+      <c r="A35" s="224"/>
+      <c r="B35" s="271" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="274"/>
-      <c r="D35" s="274"/>
-      <c r="E35" s="275"/>
-      <c r="F35" s="286"/>
-      <c r="G35" s="287"/>
-      <c r="H35" s="287"/>
-      <c r="I35" s="288"/>
-      <c r="J35" s="243"/>
-      <c r="K35" s="158"/>
-      <c r="L35" s="211"/>
+      <c r="C35" s="272"/>
+      <c r="D35" s="272"/>
+      <c r="E35" s="273"/>
+      <c r="F35" s="284"/>
+      <c r="G35" s="285"/>
+      <c r="H35" s="285"/>
+      <c r="I35" s="286"/>
+      <c r="J35" s="241"/>
+      <c r="K35" s="182"/>
+      <c r="L35" s="209"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="226"/>
-      <c r="B36" s="264" t="s">
+      <c r="A36" s="224"/>
+      <c r="B36" s="262" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="265"/>
-      <c r="D36" s="265"/>
-      <c r="E36" s="266"/>
-      <c r="F36" s="259" t="s">
+      <c r="C36" s="263"/>
+      <c r="D36" s="263"/>
+      <c r="E36" s="264"/>
+      <c r="F36" s="257" t="s">
         <v>131</v>
       </c>
-      <c r="G36" s="260"/>
-      <c r="H36" s="260"/>
-      <c r="I36" s="261"/>
-      <c r="J36" s="243"/>
-      <c r="K36" s="158"/>
-      <c r="L36" s="211"/>
+      <c r="G36" s="258"/>
+      <c r="H36" s="258"/>
+      <c r="I36" s="259"/>
+      <c r="J36" s="241"/>
+      <c r="K36" s="182"/>
+      <c r="L36" s="209"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="226"/>
-      <c r="B37" s="256" t="s">
+      <c r="A37" s="224"/>
+      <c r="B37" s="254" t="s">
         <v>132</v>
       </c>
-      <c r="C37" s="257"/>
-      <c r="D37" s="257"/>
-      <c r="E37" s="258"/>
-      <c r="F37" s="259" t="s">
+      <c r="C37" s="255"/>
+      <c r="D37" s="255"/>
+      <c r="E37" s="256"/>
+      <c r="F37" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="G37" s="260"/>
-      <c r="H37" s="260"/>
-      <c r="I37" s="261"/>
-      <c r="J37" s="243"/>
-      <c r="K37" s="158"/>
-      <c r="L37" s="211"/>
+      <c r="G37" s="258"/>
+      <c r="H37" s="258"/>
+      <c r="I37" s="259"/>
+      <c r="J37" s="241"/>
+      <c r="K37" s="182"/>
+      <c r="L37" s="209"/>
     </row>
     <row r="38" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A38" s="226"/>
-      <c r="B38" s="256" t="s">
+      <c r="A38" s="224"/>
+      <c r="B38" s="254" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="257"/>
-      <c r="D38" s="257"/>
-      <c r="E38" s="258"/>
-      <c r="F38" s="259" t="s">
+      <c r="C38" s="255"/>
+      <c r="D38" s="255"/>
+      <c r="E38" s="256"/>
+      <c r="F38" s="257" t="s">
         <v>134</v>
       </c>
-      <c r="G38" s="262"/>
-      <c r="H38" s="262"/>
-      <c r="I38" s="263"/>
-      <c r="J38" s="243"/>
-      <c r="K38" s="158"/>
-      <c r="L38" s="211"/>
+      <c r="G38" s="260"/>
+      <c r="H38" s="260"/>
+      <c r="I38" s="261"/>
+      <c r="J38" s="241"/>
+      <c r="K38" s="182"/>
+      <c r="L38" s="209"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="227"/>
-      <c r="B39" s="264" t="s">
+      <c r="A39" s="225"/>
+      <c r="B39" s="262" t="s">
         <v>73</v>
       </c>
-      <c r="C39" s="265"/>
-      <c r="D39" s="265"/>
-      <c r="E39" s="266"/>
-      <c r="F39" s="259" t="s">
+      <c r="C39" s="263"/>
+      <c r="D39" s="263"/>
+      <c r="E39" s="264"/>
+      <c r="F39" s="257" t="s">
         <v>135</v>
       </c>
-      <c r="G39" s="260"/>
-      <c r="H39" s="260"/>
-      <c r="I39" s="261"/>
-      <c r="J39" s="243"/>
-      <c r="K39" s="158"/>
-      <c r="L39" s="211"/>
+      <c r="G39" s="258"/>
+      <c r="H39" s="258"/>
+      <c r="I39" s="259"/>
+      <c r="J39" s="241"/>
+      <c r="K39" s="182"/>
+      <c r="L39" s="209"/>
     </row>
     <row r="40" spans="1:12" ht="18" customHeight="1">
-      <c r="A40" s="244" t="s">
+      <c r="A40" s="242" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="245"/>
-      <c r="C40" s="246"/>
-      <c r="D40" s="247" t="s">
+      <c r="B40" s="243"/>
+      <c r="C40" s="244"/>
+      <c r="D40" s="245" t="s">
         <v>136</v>
       </c>
-      <c r="E40" s="248"/>
-      <c r="F40" s="248"/>
-      <c r="G40" s="248"/>
-      <c r="H40" s="248"/>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="246"/>
+      <c r="H40" s="246"/>
       <c r="I40" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J40" s="279"/>
-      <c r="K40" s="280"/>
-      <c r="L40" s="281"/>
+      <c r="J40" s="277"/>
+      <c r="K40" s="278"/>
+      <c r="L40" s="279"/>
     </row>
     <row r="41" spans="1:12" ht="17.25" customHeight="1">
       <c r="A41" s="1"/>
@@ -6336,11 +6349,11 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="278" t="s">
+      <c r="J41" s="276" t="s">
         <v>137</v>
       </c>
-      <c r="K41" s="158"/>
-      <c r="L41" s="158"/>
+      <c r="K41" s="182"/>
+      <c r="L41" s="182"/>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="2"/>
